--- a/data/trans_camb/P43-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P43-Estudios-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16,29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,88</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,4</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17,88</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17,4</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,02; 20,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,57; 21,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,43; 21,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 19,97</t>
+          <t>12,02; 20,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,78; 22,17</t>
+          <t>13,57; 21,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 21,3</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,13; 19,97</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13,78; 22,17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13,03; 21,3</t>
+          <t>13,43; 21,93</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37,57%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36,58%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,49; 44,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,42; 49,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,34; 48,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,25; 43,62</t>
+          <t>24,49; 44,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,64; 48,26</t>
+          <t>27,42; 49,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 46,55</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,25; 43,62</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27,64; 48,26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26,02; 46,55</t>
+          <t>27,34; 48,19</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,9</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21,72</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,72</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,04</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12,9</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>21,72</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,69; 10,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,62; 16,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,74; 37,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,77</t>
+          <t>3,69; 10,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 16,2</t>
+          <t>9,62; 16,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,01; 38,46</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,86; 10,77</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,38; 16,2</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13,01; 38,46</t>
+          <t>13,74; 37,59</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42,27%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>71,19%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,65; 35,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,68; 55,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,33; 130,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 37,53</t>
+          <t>11,65; 35,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,01; 56,33</t>
+          <t>29,68; 55,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,87; 134,47</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,29; 37,53</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>29,01; 56,33</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>41,87; 134,47</t>
+          <t>44,33; 130,63</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22,06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,06</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22,06</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,26; 5,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,05; 15,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,01; 27,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 5,93</t>
+          <t>-7,26; 5,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,94</t>
+          <t>3,05; 15,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,27; 28,05</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-8,07; 5,93</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3,48; 15,94</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16,27; 28,05</t>
+          <t>16,01; 27,78</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,45%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-2,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>26,19%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>61,45%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,07; 16,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,97; 46,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,98; 85,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 17,64</t>
+          <t>-19,07; 16,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 48,88</t>
+          <t>7,97; 46,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,42; 85,91</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-21,17; 17,64</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>8,64; 48,88</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>40,42; 85,91</t>
+          <t>40,98; 85,37</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,99</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,02</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,23</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11,99</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>18,02</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,86; 11,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,59; 14,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,08; 27,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,54</t>
+          <t>6,86; 11,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,47; 14,27</t>
+          <t>9,59; 14,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,19; 29,38</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,7; 11,54</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>9,47; 14,27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>13,19; 29,38</t>
+          <t>13,08; 27,4</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>47,55%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47,55%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,54; 31,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,17; 38,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,98; 72,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,12; 31,23</t>
+          <t>17,54; 31,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,82; 38,74</t>
+          <t>24,17; 38,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,37; 77,61</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,12; 31,23</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23,82; 38,74</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>34,37; 77,61</t>
+          <t>33,98; 72,34</t>
         </is>
       </c>
     </row>
@@ -1483,13 +1215,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>
   </mergeCells>

--- a/data/trans_camb/P43-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P43-Estudios-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>17,13</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,4</t>
+          <t>17,13</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 20,01</t>
+          <t>12,57; 20,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 21,95</t>
+          <t>13,65; 22,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,43; 21,93</t>
+          <t>12,89; 21,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 20,01</t>
+          <t>12,57; 20,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 21,95</t>
+          <t>13,65; 22,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,43; 21,93</t>
+          <t>12,89; 21,18</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,49; 44,38</t>
+          <t>24,75; 44,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,42; 49,39</t>
+          <t>27,12; 48,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,34; 48,19</t>
+          <t>26,06; 46,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,49; 44,38</t>
+          <t>24,75; 44,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,42; 49,39</t>
+          <t>27,12; 48,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,34; 48,19</t>
+          <t>26,06; 46,57</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21,72</t>
+          <t>14,73</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,72</t>
+          <t>14,73</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,19</t>
+          <t>3,81; 10,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 16,22</t>
+          <t>9,85; 16,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 37,59</t>
+          <t>11,23; 17,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,19</t>
+          <t>3,81; 10,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 16,22</t>
+          <t>9,85; 16,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,74; 37,59</t>
+          <t>11,23; 17,81</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>48,29%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 35,85</t>
+          <t>11,86; 36,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 55,93</t>
+          <t>30,65; 58,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,33; 130,63</t>
+          <t>34,44; 61,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 35,85</t>
+          <t>11,86; 36,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 55,93</t>
+          <t>30,65; 58,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,33; 130,63</t>
+          <t>34,44; 61,92</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,06</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,06</t>
+          <t>22,5</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,51</t>
+          <t>-7,0; 5,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 15,19</t>
+          <t>3,3; 15,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 27,78</t>
+          <t>16,24; 28,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,51</t>
+          <t>-7,0; 5,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 15,19</t>
+          <t>3,3; 15,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 27,78</t>
+          <t>16,24; 28,54</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 16,99</t>
+          <t>-17,97; 18,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,97; 46,03</t>
+          <t>8,77; 48,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,98; 85,37</t>
+          <t>41,69; 90,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 16,99</t>
+          <t>-17,97; 18,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,97; 46,03</t>
+          <t>8,77; 48,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,98; 85,37</t>
+          <t>41,69; 90,6</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,38</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,5</t>
+          <t>6,78; 11,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 14,26</t>
+          <t>9,87; 14,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,08; 27,4</t>
+          <t>12,22; 16,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,5</t>
+          <t>6,78; 11,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 14,26</t>
+          <t>9,87; 14,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,08; 27,4</t>
+          <t>12,22; 16,75</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,54; 31,23</t>
+          <t>17,66; 32,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,17; 38,58</t>
+          <t>25,29; 39,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,98; 72,34</t>
+          <t>31,26; 45,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,54; 31,23</t>
+          <t>17,66; 32,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,17; 38,58</t>
+          <t>25,29; 39,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,98; 72,34</t>
+          <t>31,26; 45,81</t>
         </is>
       </c>
     </row>
